--- a/src/data/calibration_data_yellow.xlsx
+++ b/src/data/calibration_data_yellow.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Matthew Tan\Documents\ECSE211\ECSE211_W26_Final_Project\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{5A3A3AB6-EC06-4CE0-9968-CCA08B0F6285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C90C640-8F29-41A3-9E22-2D4027343475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1DF4A7C3-7D68-400B-AB8D-102D5F0D741C}"/>
   </bookViews>
   <sheets>
     <sheet name="calibration_data_yellow" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>R</t>
   </si>
@@ -31,10 +44,16 @@
     <t>B</t>
   </si>
   <si>
-    <t>avg</t>
+    <t>vector avg</t>
   </si>
   <si>
-    <t>std dev</t>
+    <t>vector std dev</t>
+  </si>
+  <si>
+    <t>ratio avg</t>
+  </si>
+  <si>
+    <t>ratio std dev</t>
   </si>
 </sst>
 </file>
@@ -42,7 +61,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="174" formatCode="0.00000000000"/>
+    <numFmt numFmtId="164" formatCode="0.00000000000"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -523,7 +542,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -899,13 +918,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6687EB2D-045A-4AFC-B834-5A2EA75A8416}">
-  <dimension ref="A1:L90"/>
+  <dimension ref="A1:P90"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="12" max="12" width="21.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -916,7 +935,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>75</v>
       </c>
@@ -938,23 +957,35 @@
         <f t="shared" si="0"/>
         <v>2.0057945174949856E-3</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2">
+        <f>A2/($A2+$B2+$C2)</f>
+        <v>0.5067567567567568</v>
+      </c>
+      <c r="J2">
+        <f t="shared" ref="J2:K2" si="1">B2/($A2+$B2+$C2)</f>
+        <v>0.3716216216216216</v>
+      </c>
+      <c r="K2">
+        <f t="shared" si="1"/>
+        <v>0.12162162162162163</v>
+      </c>
+      <c r="M2" t="s">
         <v>3</v>
       </c>
-      <c r="J2">
+      <c r="N2">
         <f>AVERAGE(E2:E90)</f>
         <v>8.0486417889068379E-3</v>
       </c>
-      <c r="K2">
-        <f t="shared" ref="K2:L2" si="1">AVERAGE(F2:F90)</f>
+      <c r="O2">
+        <f>AVERAGE(F2:F90)</f>
         <v>5.9093857290239398E-3</v>
       </c>
-      <c r="L2">
-        <f t="shared" si="1"/>
+      <c r="P2">
+        <f>AVERAGE(G2:G90)</f>
         <v>2.0817294711076169E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>77</v>
       </c>
@@ -976,23 +1007,35 @@
         <f t="shared" ref="G3:G66" si="4">C3/($A3^2 + $B3^2 + $C3^2)</f>
         <v>2.0633446817290828E-3</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3">
+        <f t="shared" ref="I3:I66" si="5">A3/($A3+$B3+$C3)</f>
+        <v>0.49677419354838709</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J66" si="6">B3/($A3+$B3+$C3)</f>
+        <v>0.37419354838709679</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K66" si="7">C3/($A3+$B3+$C3)</f>
+        <v>0.12903225806451613</v>
+      </c>
+      <c r="M3" t="s">
         <v>4</v>
       </c>
-      <c r="J3">
+      <c r="N3">
         <f>_xlfn.STDEV.P(E2:E90)</f>
         <v>1.8566429468514192E-4</v>
       </c>
-      <c r="K3">
-        <f t="shared" ref="K3:L3" si="5">_xlfn.STDEV.P(F2:F90)</f>
+      <c r="O3">
+        <f>_xlfn.STDEV.P(F2:F90)</f>
         <v>1.2930839973084404E-4</v>
       </c>
-      <c r="L3" s="1">
-        <f t="shared" si="5"/>
+      <c r="P3" s="1">
+        <f>_xlfn.STDEV.P(G2:G90)</f>
         <v>7.1667382718370332E-5</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>77</v>
       </c>
@@ -1014,8 +1057,20 @@
         <f t="shared" si="4"/>
         <v>2.1573864803780562E-3</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I4">
+        <f t="shared" si="5"/>
+        <v>0.49358974358974361</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="6"/>
+        <v>0.37179487179487181</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="7"/>
+        <v>0.13461538461538461</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>78</v>
       </c>
@@ -1037,8 +1092,35 @@
         <f t="shared" si="4"/>
         <v>2.0790020790020791E-3</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I5">
+        <f t="shared" si="5"/>
+        <v>0.50649350649350644</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="6"/>
+        <v>0.36363636363636365</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="7"/>
+        <v>0.12987012987012986</v>
+      </c>
+      <c r="M5" t="s">
+        <v>5</v>
+      </c>
+      <c r="N5">
+        <f>AVERAGE(I2:I90)</f>
+        <v>0.50176977585373539</v>
+      </c>
+      <c r="O5">
+        <f t="shared" ref="O5:P5" si="8">AVERAGE(J2:J90)</f>
+        <v>0.36841182695312352</v>
+      </c>
+      <c r="P5">
+        <f t="shared" si="8"/>
+        <v>0.12981839719314101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>78</v>
       </c>
@@ -1060,8 +1142,35 @@
         <f t="shared" si="4"/>
         <v>2.0548648926333093E-3</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I6">
+        <f t="shared" si="5"/>
+        <v>0.50322580645161286</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="6"/>
+        <v>0.36774193548387096</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="7"/>
+        <v>0.12903225806451613</v>
+      </c>
+      <c r="M6" t="s">
+        <v>6</v>
+      </c>
+      <c r="N6">
+        <f>_xlfn.STDEV.P(I2:I90)</f>
+        <v>4.7526313954907532E-3</v>
+      </c>
+      <c r="O6">
+        <f t="shared" ref="O6:P6" si="9">_xlfn.STDEV.P(J2:J90)</f>
+        <v>3.4872864442641702E-3</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="9"/>
+        <v>4.7732916401148854E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>76</v>
       </c>
@@ -1083,8 +1192,20 @@
         <f t="shared" si="4"/>
         <v>2.1736767742636669E-3</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I7">
+        <f t="shared" si="5"/>
+        <v>0.50331125827814571</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="6"/>
+        <v>0.36423841059602646</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="7"/>
+        <v>0.13245033112582782</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>76</v>
       </c>
@@ -1106,8 +1227,20 @@
         <f t="shared" si="4"/>
         <v>1.9726027397260273E-3</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I8">
+        <f t="shared" si="5"/>
+        <v>0.51006711409395977</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="6"/>
+        <v>0.36912751677852351</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="7"/>
+        <v>0.12080536912751678</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>77</v>
       </c>
@@ -1129,8 +1262,20 @@
         <f t="shared" si="4"/>
         <v>2.0881186051367718E-3</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I9">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="6"/>
+        <v>0.37012987012987014</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="7"/>
+        <v>0.12987012987012986</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>78</v>
       </c>
@@ -1152,8 +1297,20 @@
         <f t="shared" si="4"/>
         <v>2.1485573971761819E-3</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I10">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="6"/>
+        <v>0.36538461538461536</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="7"/>
+        <v>0.13461538461538461</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>81</v>
       </c>
@@ -1175,8 +1332,20 @@
         <f t="shared" si="4"/>
         <v>2.285496619369584E-3</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I11">
+        <f t="shared" si="5"/>
+        <v>0.49693251533742333</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="6"/>
+        <v>0.35582822085889571</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="7"/>
+        <v>0.14723926380368099</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>77</v>
       </c>
@@ -1198,8 +1367,20 @@
         <f t="shared" si="4"/>
         <v>2.0157012518565668E-3</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I12">
+        <f t="shared" si="5"/>
+        <v>0.50657894736842102</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="6"/>
+        <v>0.36842105263157893</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="7"/>
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>78</v>
       </c>
@@ -1221,8 +1402,20 @@
         <f t="shared" si="4"/>
         <v>2.1235716452624128E-3</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I13">
+        <f t="shared" si="5"/>
+        <v>0.49681528662420382</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="6"/>
+        <v>0.36942675159235666</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="7"/>
+        <v>0.13375796178343949</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>75</v>
       </c>
@@ -1244,8 +1437,20 @@
         <f t="shared" si="4"/>
         <v>2.2099447513812156E-3</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I14">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="6"/>
+        <v>0.36666666666666664</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="7"/>
+        <v>0.13333333333333333</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>77</v>
       </c>
@@ -1267,8 +1472,20 @@
         <f t="shared" si="4"/>
         <v>1.917137075300884E-3</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I15">
+        <f t="shared" si="5"/>
+        <v>0.50993377483443714</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="6"/>
+        <v>0.37086092715231789</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="7"/>
+        <v>0.11920529801324503</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>77</v>
       </c>
@@ -1290,8 +1507,20 @@
         <f t="shared" si="4"/>
         <v>2.1831791246491321E-3</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I16">
+        <f t="shared" si="5"/>
+        <v>0.49677419354838709</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="6"/>
+        <v>0.36774193548387096</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="7"/>
+        <v>0.13548387096774195</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>76</v>
       </c>
@@ -1313,8 +1542,20 @@
         <f t="shared" si="4"/>
         <v>2.1477663230240552E-3</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I17">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="6"/>
+        <v>0.36842105263157893</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="7"/>
+        <v>0.13157894736842105</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>78</v>
       </c>
@@ -1336,8 +1577,20 @@
         <f t="shared" si="4"/>
         <v>1.9830915353303414E-3</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I18">
+        <f t="shared" si="5"/>
+        <v>0.50980392156862742</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="6"/>
+        <v>0.36601307189542481</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="7"/>
+        <v>0.12418300653594772</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>77</v>
       </c>
@@ -1359,8 +1612,20 @@
         <f t="shared" si="4"/>
         <v>2.0881186051367718E-3</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I19">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="6"/>
+        <v>0.37012987012987014</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="7"/>
+        <v>0.12987012987012986</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>77</v>
       </c>
@@ -1382,8 +1647,20 @@
         <f t="shared" si="4"/>
         <v>2.1573864803780562E-3</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I20">
+        <f t="shared" si="5"/>
+        <v>0.49358974358974361</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="6"/>
+        <v>0.37179487179487181</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="7"/>
+        <v>0.13461538461538461</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>78</v>
       </c>
@@ -1405,8 +1682,20 @@
         <f t="shared" si="4"/>
         <v>2.0548648926333093E-3</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I21">
+        <f t="shared" si="5"/>
+        <v>0.50322580645161286</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="6"/>
+        <v>0.36774193548387096</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="7"/>
+        <v>0.12903225806451613</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>78</v>
       </c>
@@ -1428,8 +1717,20 @@
         <f t="shared" si="4"/>
         <v>1.9599752424179907E-3</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I22">
+        <f t="shared" si="5"/>
+        <v>0.50649350649350644</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="6"/>
+        <v>0.37012987012987014</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="7"/>
+        <v>0.12337662337662338</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>77</v>
       </c>
@@ -1451,8 +1752,20 @@
         <f t="shared" si="4"/>
         <v>2.0881186051367718E-3</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I23">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="6"/>
+        <v>0.37012987012987014</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="7"/>
+        <v>0.12987012987012986</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>78</v>
       </c>
@@ -1474,8 +1787,20 @@
         <f t="shared" si="4"/>
         <v>2.0790020790020791E-3</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I24">
+        <f t="shared" si="5"/>
+        <v>0.50649350649350644</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="6"/>
+        <v>0.36363636363636365</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="7"/>
+        <v>0.12987012987012986</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>76</v>
       </c>
@@ -1497,8 +1822,20 @@
         <f t="shared" si="4"/>
         <v>2.1477663230240552E-3</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I25">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="6"/>
+        <v>0.36842105263157893</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="7"/>
+        <v>0.13157894736842105</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>77</v>
       </c>
@@ -1520,8 +1857,20 @@
         <f t="shared" si="4"/>
         <v>1.9400732916576848E-3</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I26">
+        <f t="shared" si="5"/>
+        <v>0.51333333333333331</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="6"/>
+        <v>0.36666666666666664</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="7"/>
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>76</v>
       </c>
@@ -1543,8 +1892,20 @@
         <f t="shared" si="4"/>
         <v>2.1736767742636669E-3</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I27">
+        <f t="shared" si="5"/>
+        <v>0.50331125827814571</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="6"/>
+        <v>0.36423841059602646</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="7"/>
+        <v>0.13245033112582782</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>80</v>
       </c>
@@ -1566,8 +1927,20 @@
         <f t="shared" si="4"/>
         <v>2.0344894400310017E-3</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I28">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="J28">
+        <f t="shared" si="6"/>
+        <v>0.36875000000000002</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="7"/>
+        <v>0.13125000000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>76</v>
       </c>
@@ -1589,8 +1962,20 @@
         <f t="shared" si="4"/>
         <v>2.1477663230240552E-3</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I29">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="J29">
+        <f t="shared" si="6"/>
+        <v>0.36842105263157893</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="7"/>
+        <v>0.13157894736842105</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>78</v>
       </c>
@@ -1612,8 +1997,20 @@
         <f t="shared" si="4"/>
         <v>2.0548648926333093E-3</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I30">
+        <f t="shared" si="5"/>
+        <v>0.50322580645161286</v>
+      </c>
+      <c r="J30">
+        <f t="shared" si="6"/>
+        <v>0.36774193548387096</v>
+      </c>
+      <c r="K30">
+        <f t="shared" si="7"/>
+        <v>0.12903225806451613</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>76</v>
       </c>
@@ -1635,8 +2032,20 @@
         <f t="shared" si="4"/>
         <v>2.1477663230240552E-3</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I31">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="J31">
+        <f t="shared" si="6"/>
+        <v>0.36842105263157893</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="7"/>
+        <v>0.13157894736842105</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>77</v>
       </c>
@@ -1658,8 +2067,20 @@
         <f t="shared" si="4"/>
         <v>2.0633446817290828E-3</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I32">
+        <f t="shared" si="5"/>
+        <v>0.49677419354838709</v>
+      </c>
+      <c r="J32">
+        <f t="shared" si="6"/>
+        <v>0.37419354838709679</v>
+      </c>
+      <c r="K32">
+        <f t="shared" si="7"/>
+        <v>0.12903225806451613</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>75</v>
       </c>
@@ -1681,8 +2102,20 @@
         <f t="shared" si="4"/>
         <v>2.1343518310492026E-3</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I33">
+        <f t="shared" si="5"/>
+        <v>0.5067567567567568</v>
+      </c>
+      <c r="J33">
+        <f t="shared" si="6"/>
+        <v>0.36486486486486486</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="7"/>
+        <v>0.12837837837837837</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>77</v>
       </c>
@@ -1704,8 +2137,20 @@
         <f t="shared" si="4"/>
         <v>2.1130480718436345E-3</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I34">
+        <f t="shared" si="5"/>
+        <v>0.50326797385620914</v>
+      </c>
+      <c r="J34">
+        <f t="shared" si="6"/>
+        <v>0.36601307189542481</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="7"/>
+        <v>0.13071895424836602</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>77</v>
       </c>
@@ -1727,8 +2172,20 @@
         <f t="shared" si="4"/>
         <v>1.9918230422476149E-3</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I35">
+        <f t="shared" si="5"/>
+        <v>0.50326797385620914</v>
+      </c>
+      <c r="J35">
+        <f t="shared" si="6"/>
+        <v>0.37254901960784315</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="7"/>
+        <v>0.12418300653594772</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>77</v>
       </c>
@@ -1750,8 +2207,20 @@
         <f t="shared" si="4"/>
         <v>2.0157012518565668E-3</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I36">
+        <f t="shared" si="5"/>
+        <v>0.50657894736842102</v>
+      </c>
+      <c r="J36">
+        <f t="shared" si="6"/>
+        <v>0.36842105263157893</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="7"/>
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>77</v>
       </c>
@@ -1773,8 +2242,20 @@
         <f t="shared" si="4"/>
         <v>2.0397208803005903E-3</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I37">
+        <f t="shared" si="5"/>
+        <v>0.50993377483443714</v>
+      </c>
+      <c r="J37">
+        <f t="shared" si="6"/>
+        <v>0.36423841059602646</v>
+      </c>
+      <c r="K37">
+        <f t="shared" si="7"/>
+        <v>0.12582781456953643</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>75</v>
       </c>
@@ -1796,8 +2277,20 @@
         <f t="shared" si="4"/>
         <v>2.1085340139829099E-3</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I38">
+        <f t="shared" si="5"/>
+        <v>0.50335570469798663</v>
+      </c>
+      <c r="J38">
+        <f t="shared" si="6"/>
+        <v>0.36912751677852351</v>
+      </c>
+      <c r="K38">
+        <f t="shared" si="7"/>
+        <v>0.12751677852348994</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>76</v>
       </c>
@@ -1819,8 +2312,20 @@
         <f t="shared" si="4"/>
         <v>2.2452688976798887E-3</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I39">
+        <f t="shared" si="5"/>
+        <v>0.49673202614379086</v>
+      </c>
+      <c r="J39">
+        <f t="shared" si="6"/>
+        <v>0.36601307189542481</v>
+      </c>
+      <c r="K39">
+        <f t="shared" si="7"/>
+        <v>0.13725490196078433</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>77</v>
       </c>
@@ -1842,8 +2347,20 @@
         <f t="shared" si="4"/>
         <v>2.0157012518565668E-3</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I40">
+        <f t="shared" si="5"/>
+        <v>0.50657894736842102</v>
+      </c>
+      <c r="J40">
+        <f t="shared" si="6"/>
+        <v>0.36842105263157893</v>
+      </c>
+      <c r="K40">
+        <f t="shared" si="7"/>
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>76</v>
       </c>
@@ -1865,8 +2382,20 @@
         <f t="shared" si="4"/>
         <v>2.1220159151193632E-3</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I41">
+        <f t="shared" si="5"/>
+        <v>0.49673202614379086</v>
+      </c>
+      <c r="J41">
+        <f t="shared" si="6"/>
+        <v>0.37254901960784315</v>
+      </c>
+      <c r="K41">
+        <f t="shared" si="7"/>
+        <v>0.13071895424836602</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>76</v>
       </c>
@@ -1888,8 +2417,20 @@
         <f t="shared" si="4"/>
         <v>2.0737830168085572E-3</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I42">
+        <f t="shared" si="5"/>
+        <v>0.50666666666666671</v>
+      </c>
+      <c r="J42">
+        <f t="shared" si="6"/>
+        <v>0.36666666666666664</v>
+      </c>
+      <c r="K42">
+        <f t="shared" si="7"/>
+        <v>0.12666666666666668</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>78</v>
       </c>
@@ -1911,8 +2452,20 @@
         <f t="shared" si="4"/>
         <v>2.0548648926333093E-3</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I43">
+        <f t="shared" si="5"/>
+        <v>0.50322580645161286</v>
+      </c>
+      <c r="J43">
+        <f t="shared" si="6"/>
+        <v>0.36774193548387096</v>
+      </c>
+      <c r="K43">
+        <f t="shared" si="7"/>
+        <v>0.12903225806451613</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>78</v>
       </c>
@@ -1934,8 +2487,20 @@
         <f t="shared" si="4"/>
         <v>2.0308692120227455E-3</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I44">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="J44">
+        <f t="shared" si="6"/>
+        <v>0.37179487179487181</v>
+      </c>
+      <c r="K44">
+        <f t="shared" si="7"/>
+        <v>0.12820512820512819</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>78</v>
       </c>
@@ -1957,8 +2522,20 @@
         <f t="shared" si="4"/>
         <v>2.0548648926333093E-3</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I45">
+        <f t="shared" si="5"/>
+        <v>0.50322580645161286</v>
+      </c>
+      <c r="J45">
+        <f t="shared" si="6"/>
+        <v>0.36774193548387096</v>
+      </c>
+      <c r="K45">
+        <f t="shared" si="7"/>
+        <v>0.12903225806451613</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>75</v>
       </c>
@@ -1980,8 +2557,20 @@
         <f t="shared" si="4"/>
         <v>2.1085340139829099E-3</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I46">
+        <f t="shared" si="5"/>
+        <v>0.50335570469798663</v>
+      </c>
+      <c r="J46">
+        <f t="shared" si="6"/>
+        <v>0.36912751677852351</v>
+      </c>
+      <c r="K46">
+        <f t="shared" si="7"/>
+        <v>0.12751677852348994</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>76</v>
       </c>
@@ -2003,8 +2592,20 @@
         <f t="shared" si="4"/>
         <v>2.1477663230240552E-3</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I47">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="J47">
+        <f t="shared" si="6"/>
+        <v>0.36842105263157893</v>
+      </c>
+      <c r="K47">
+        <f t="shared" si="7"/>
+        <v>0.13157894736842105</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>76</v>
       </c>
@@ -2026,8 +2627,20 @@
         <f t="shared" si="4"/>
         <v>2.1477663230240552E-3</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I48">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="J48">
+        <f t="shared" si="6"/>
+        <v>0.36842105263157893</v>
+      </c>
+      <c r="K48">
+        <f t="shared" si="7"/>
+        <v>0.13157894736842105</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>76</v>
       </c>
@@ -2049,8 +2662,20 @@
         <f t="shared" si="4"/>
         <v>2.1477663230240552E-3</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I49">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="J49">
+        <f t="shared" si="6"/>
+        <v>0.36842105263157893</v>
+      </c>
+      <c r="K49">
+        <f t="shared" si="7"/>
+        <v>0.13157894736842105</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>77</v>
       </c>
@@ -2072,8 +2697,20 @@
         <f t="shared" si="4"/>
         <v>2.0157012518565668E-3</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I50">
+        <f t="shared" si="5"/>
+        <v>0.50657894736842102</v>
+      </c>
+      <c r="J50">
+        <f t="shared" si="6"/>
+        <v>0.36842105263157893</v>
+      </c>
+      <c r="K50">
+        <f t="shared" si="7"/>
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>78</v>
       </c>
@@ -2095,8 +2732,20 @@
         <f t="shared" si="4"/>
         <v>2.1485573971761819E-3</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I51">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="J51">
+        <f t="shared" si="6"/>
+        <v>0.36538461538461536</v>
+      </c>
+      <c r="K51">
+        <f t="shared" si="7"/>
+        <v>0.13461538461538461</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>75</v>
       </c>
@@ -2118,8 +2767,20 @@
         <f t="shared" si="4"/>
         <v>2.1085340139829099E-3</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I52">
+        <f t="shared" si="5"/>
+        <v>0.50335570469798663</v>
+      </c>
+      <c r="J52">
+        <f t="shared" si="6"/>
+        <v>0.36912751677852351</v>
+      </c>
+      <c r="K52">
+        <f t="shared" si="7"/>
+        <v>0.12751677852348994</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>76</v>
       </c>
@@ -2141,8 +2802,20 @@
         <f t="shared" si="4"/>
         <v>2.1477663230240552E-3</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I53">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="J53">
+        <f t="shared" si="6"/>
+        <v>0.36842105263157893</v>
+      </c>
+      <c r="K53">
+        <f t="shared" si="7"/>
+        <v>0.13157894736842105</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>79</v>
       </c>
@@ -2164,8 +2837,20 @@
         <f t="shared" si="4"/>
         <v>2.1555947481873409E-3</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I54">
+        <f t="shared" si="5"/>
+        <v>0.49375000000000002</v>
+      </c>
+      <c r="J54">
+        <f t="shared" si="6"/>
+        <v>0.36875000000000002</v>
+      </c>
+      <c r="K54">
+        <f t="shared" si="7"/>
+        <v>0.13750000000000001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>77</v>
       </c>
@@ -2187,8 +2872,20 @@
         <f t="shared" si="4"/>
         <v>2.0157012518565668E-3</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I55">
+        <f t="shared" si="5"/>
+        <v>0.50657894736842102</v>
+      </c>
+      <c r="J55">
+        <f t="shared" si="6"/>
+        <v>0.36842105263157893</v>
+      </c>
+      <c r="K55">
+        <f t="shared" si="7"/>
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>77</v>
       </c>
@@ -2210,8 +2907,20 @@
         <f t="shared" si="4"/>
         <v>2.0397208803005903E-3</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I56">
+        <f t="shared" si="5"/>
+        <v>0.50993377483443714</v>
+      </c>
+      <c r="J56">
+        <f t="shared" si="6"/>
+        <v>0.36423841059602646</v>
+      </c>
+      <c r="K56">
+        <f t="shared" si="7"/>
+        <v>0.12582781456953643</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>76</v>
       </c>
@@ -2233,8 +2942,20 @@
         <f t="shared" si="4"/>
         <v>2.04895934433301E-3</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I57">
+        <f t="shared" si="5"/>
+        <v>0.50331125827814571</v>
+      </c>
+      <c r="J57">
+        <f t="shared" si="6"/>
+        <v>0.37086092715231789</v>
+      </c>
+      <c r="K57">
+        <f t="shared" si="7"/>
+        <v>0.12582781456953643</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>78</v>
       </c>
@@ -2256,8 +2977,20 @@
         <f t="shared" si="4"/>
         <v>1.9599752424179907E-3</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I58">
+        <f t="shared" si="5"/>
+        <v>0.50649350649350644</v>
+      </c>
+      <c r="J58">
+        <f t="shared" si="6"/>
+        <v>0.37012987012987014</v>
+      </c>
+      <c r="K58">
+        <f t="shared" si="7"/>
+        <v>0.12337662337662338</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>78</v>
       </c>
@@ -2279,8 +3012,20 @@
         <f t="shared" si="4"/>
         <v>2.0308692120227455E-3</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I59">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="J59">
+        <f t="shared" si="6"/>
+        <v>0.37179487179487181</v>
+      </c>
+      <c r="K59">
+        <f t="shared" si="7"/>
+        <v>0.12820512820512819</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>76</v>
       </c>
@@ -2302,8 +3047,20 @@
         <f t="shared" si="4"/>
         <v>2.04895934433301E-3</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I60">
+        <f t="shared" si="5"/>
+        <v>0.50331125827814571</v>
+      </c>
+      <c r="J60">
+        <f t="shared" si="6"/>
+        <v>0.37086092715231789</v>
+      </c>
+      <c r="K60">
+        <f t="shared" si="7"/>
+        <v>0.12582781456953643</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>78</v>
       </c>
@@ -2325,8 +3082,20 @@
         <f t="shared" si="4"/>
         <v>2.1235716452624128E-3</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I61">
+        <f t="shared" si="5"/>
+        <v>0.49681528662420382</v>
+      </c>
+      <c r="J61">
+        <f t="shared" si="6"/>
+        <v>0.36942675159235666</v>
+      </c>
+      <c r="K61">
+        <f t="shared" si="7"/>
+        <v>0.13375796178343949</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>79</v>
       </c>
@@ -2348,8 +3117,20 @@
         <f t="shared" si="4"/>
         <v>1.9758940920766646E-3</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I62">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="J62">
+        <f t="shared" si="6"/>
+        <v>0.37341772151898733</v>
+      </c>
+      <c r="K62">
+        <f t="shared" si="7"/>
+        <v>0.12658227848101267</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>79</v>
       </c>
@@ -2371,8 +3152,20 @@
         <f t="shared" si="4"/>
         <v>2.1555947481873409E-3</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I63">
+        <f t="shared" si="5"/>
+        <v>0.49375000000000002</v>
+      </c>
+      <c r="J63">
+        <f t="shared" si="6"/>
+        <v>0.36875000000000002</v>
+      </c>
+      <c r="K63">
+        <f t="shared" si="7"/>
+        <v>0.13750000000000001</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>80</v>
       </c>
@@ -2394,8 +3187,20 @@
         <f t="shared" si="4"/>
         <v>2.0113015994636528E-3</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I64">
+        <f t="shared" si="5"/>
+        <v>0.49689440993788819</v>
+      </c>
+      <c r="J64">
+        <f t="shared" si="6"/>
+        <v>0.37267080745341613</v>
+      </c>
+      <c r="K64">
+        <f t="shared" si="7"/>
+        <v>0.13043478260869565</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>76</v>
       </c>
@@ -2417,8 +3222,20 @@
         <f t="shared" si="4"/>
         <v>2.1220159151193632E-3</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I65">
+        <f t="shared" si="5"/>
+        <v>0.49673202614379086</v>
+      </c>
+      <c r="J65">
+        <f t="shared" si="6"/>
+        <v>0.37254901960784315</v>
+      </c>
+      <c r="K65">
+        <f t="shared" si="7"/>
+        <v>0.13071895424836602</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>78</v>
       </c>
@@ -2440,8 +3257,20 @@
         <f t="shared" si="4"/>
         <v>2.1892725644342722E-3</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I66">
+        <f t="shared" si="5"/>
+        <v>0.49056603773584906</v>
+      </c>
+      <c r="J66">
+        <f t="shared" si="6"/>
+        <v>0.37106918238993708</v>
+      </c>
+      <c r="K66">
+        <f t="shared" si="7"/>
+        <v>0.13836477987421383</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>80</v>
       </c>
@@ -2452,19 +3281,31 @@
         <v>20</v>
       </c>
       <c r="E67">
-        <f t="shared" ref="E67:E90" si="6">A67/($A67^2 + $B67^2 + $C67^2)</f>
+        <f t="shared" ref="E67:E90" si="10">A67/($A67^2 + $B67^2 + $C67^2)</f>
         <v>7.8709169618260532E-3</v>
       </c>
       <c r="F67">
-        <f t="shared" ref="F67:F90" si="7">B67/($A67^2 + $B67^2 + $C67^2)</f>
+        <f t="shared" ref="F67:F90" si="11">B67/($A67^2 + $B67^2 + $C67^2)</f>
         <v>5.7064147973238883E-3</v>
       </c>
       <c r="G67">
-        <f t="shared" ref="G67:G90" si="8">C67/($A67^2 + $B67^2 + $C67^2)</f>
+        <f t="shared" ref="G67:G90" si="12">C67/($A67^2 + $B67^2 + $C67^2)</f>
         <v>1.9677292404565133E-3</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I67">
+        <f t="shared" ref="I67:I90" si="13">A67/($A67+$B67+$C67)</f>
+        <v>0.50632911392405067</v>
+      </c>
+      <c r="J67">
+        <f t="shared" ref="J67:J90" si="14">B67/($A67+$B67+$C67)</f>
+        <v>0.36708860759493672</v>
+      </c>
+      <c r="K67">
+        <f t="shared" ref="K67:K90" si="15">C67/($A67+$B67+$C67)</f>
+        <v>0.12658227848101267</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>77</v>
       </c>
@@ -2475,19 +3316,31 @@
         <v>20</v>
       </c>
       <c r="E68">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>8.039256629776571E-3</v>
       </c>
       <c r="F68">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>5.9511380246397997E-3</v>
       </c>
       <c r="G68">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>2.0881186051367718E-3</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I68">
+        <f t="shared" si="13"/>
+        <v>0.5</v>
+      </c>
+      <c r="J68">
+        <f t="shared" si="14"/>
+        <v>0.37012987012987014</v>
+      </c>
+      <c r="K68">
+        <f t="shared" si="15"/>
+        <v>0.12987012987012986</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>77</v>
       </c>
@@ -2498,19 +3351,31 @@
         <v>20</v>
       </c>
       <c r="E69">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>8.039256629776571E-3</v>
       </c>
       <c r="F69">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>5.9511380246397997E-3</v>
       </c>
       <c r="G69">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>2.0881186051367718E-3</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I69">
+        <f t="shared" si="13"/>
+        <v>0.5</v>
+      </c>
+      <c r="J69">
+        <f t="shared" si="14"/>
+        <v>0.37012987012987014</v>
+      </c>
+      <c r="K69">
+        <f t="shared" si="15"/>
+        <v>0.12987012987012986</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>78</v>
       </c>
@@ -2521,19 +3386,31 @@
         <v>21</v>
       </c>
       <c r="E70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>8.0736983749094288E-3</v>
       </c>
       <c r="F70">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>5.7965013973708722E-3</v>
       </c>
       <c r="G70">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>2.1736880240140772E-3</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I70">
+        <f t="shared" si="13"/>
+        <v>0.50322580645161286</v>
+      </c>
+      <c r="J70">
+        <f t="shared" si="14"/>
+        <v>0.36129032258064514</v>
+      </c>
+      <c r="K70">
+        <f t="shared" si="15"/>
+        <v>0.13548387096774195</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>79</v>
       </c>
@@ -2544,19 +3421,31 @@
         <v>20</v>
       </c>
       <c r="E71">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>7.8960519740129929E-3</v>
       </c>
       <c r="F71">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>5.7971014492753624E-3</v>
       </c>
       <c r="G71">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1.9990004997501249E-3</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I71">
+        <f t="shared" si="13"/>
+        <v>0.50318471337579618</v>
+      </c>
+      <c r="J71">
+        <f t="shared" si="14"/>
+        <v>0.36942675159235666</v>
+      </c>
+      <c r="K71">
+        <f t="shared" si="15"/>
+        <v>0.12738853503184713</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>80</v>
       </c>
@@ -2567,19 +3456,31 @@
         <v>21</v>
       </c>
       <c r="E72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>7.839294463498285E-3</v>
       </c>
       <c r="F72">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>5.6834884860362568E-3</v>
       </c>
       <c r="G72">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>2.0578147966682997E-3</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I72">
+        <f t="shared" si="13"/>
+        <v>0.50314465408805031</v>
+      </c>
+      <c r="J72">
+        <f t="shared" si="14"/>
+        <v>0.36477987421383645</v>
+      </c>
+      <c r="K72">
+        <f t="shared" si="15"/>
+        <v>0.13207547169811321</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>79</v>
       </c>
@@ -2590,19 +3491,31 @@
         <v>21</v>
       </c>
       <c r="E73">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>7.8638263985665938E-3</v>
       </c>
       <c r="F73">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>5.7734421660362335E-3</v>
       </c>
       <c r="G73">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>2.0903842325303602E-3</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I73">
+        <f t="shared" si="13"/>
+        <v>0.5</v>
+      </c>
+      <c r="J73">
+        <f t="shared" si="14"/>
+        <v>0.36708860759493672</v>
+      </c>
+      <c r="K73">
+        <f t="shared" si="15"/>
+        <v>0.13291139240506328</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>76</v>
       </c>
@@ -2613,19 +3526,31 @@
         <v>20</v>
       </c>
       <c r="E74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>8.0636604774535804E-3</v>
       </c>
       <c r="F74">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>6.0477453580901853E-3</v>
       </c>
       <c r="G74">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>2.1220159151193632E-3</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I74">
+        <f t="shared" si="13"/>
+        <v>0.49673202614379086</v>
+      </c>
+      <c r="J74">
+        <f t="shared" si="14"/>
+        <v>0.37254901960784315</v>
+      </c>
+      <c r="K74">
+        <f t="shared" si="15"/>
+        <v>0.13071895424836602</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>78</v>
       </c>
@@ -2636,19 +3561,31 @@
         <v>21</v>
       </c>
       <c r="E75">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>7.7953228063162103E-3</v>
       </c>
       <c r="F75">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>5.8964621227263645E-3</v>
       </c>
       <c r="G75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>2.0987407555466721E-3</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I75">
+        <f t="shared" si="13"/>
+        <v>0.49367088607594939</v>
+      </c>
+      <c r="J75">
+        <f t="shared" si="14"/>
+        <v>0.37341772151898733</v>
+      </c>
+      <c r="K75">
+        <f t="shared" si="15"/>
+        <v>0.13291139240506328</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>78</v>
       </c>
@@ -2659,19 +3596,31 @@
         <v>22</v>
       </c>
       <c r="E76">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>7.7619663648124193E-3</v>
       </c>
       <c r="F76">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>5.8712309682555476E-3</v>
       </c>
       <c r="G76">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>2.1892725644342722E-3</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I76">
+        <f t="shared" si="13"/>
+        <v>0.49056603773584906</v>
+      </c>
+      <c r="J76">
+        <f t="shared" si="14"/>
+        <v>0.37106918238993708</v>
+      </c>
+      <c r="K76">
+        <f t="shared" si="15"/>
+        <v>0.13836477987421383</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76</v>
       </c>
@@ -2682,19 +3631,31 @@
         <v>19</v>
       </c>
       <c r="E77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>8.2951320672342288E-3</v>
       </c>
       <c r="F77">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>6.0030561012879282E-3</v>
       </c>
       <c r="G77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>2.0737830168085572E-3</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I77">
+        <f t="shared" si="13"/>
+        <v>0.50666666666666671</v>
+      </c>
+      <c r="J77">
+        <f t="shared" si="14"/>
+        <v>0.36666666666666664</v>
+      </c>
+      <c r="K77">
+        <f t="shared" si="15"/>
+        <v>0.12666666666666668</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>79</v>
       </c>
@@ -2705,19 +3666,31 @@
         <v>20</v>
       </c>
       <c r="E78">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>7.8960519740129929E-3</v>
       </c>
       <c r="F78">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>5.7971014492753624E-3</v>
       </c>
       <c r="G78">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1.9990004997501249E-3</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I78">
+        <f t="shared" si="13"/>
+        <v>0.50318471337579618</v>
+      </c>
+      <c r="J78">
+        <f t="shared" si="14"/>
+        <v>0.36942675159235666</v>
+      </c>
+      <c r="K78">
+        <f t="shared" si="15"/>
+        <v>0.12738853503184713</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>79</v>
       </c>
@@ -2728,19 +3701,31 @@
         <v>21</v>
       </c>
       <c r="E79">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>7.7732952868247562E-3</v>
       </c>
       <c r="F79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>5.8053724294007672E-3</v>
       </c>
       <c r="G79">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>2.0663190002951884E-3</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I79">
+        <f t="shared" si="13"/>
+        <v>0.49685534591194969</v>
+      </c>
+      <c r="J79">
+        <f t="shared" si="14"/>
+        <v>0.37106918238993708</v>
+      </c>
+      <c r="K79">
+        <f t="shared" si="15"/>
+        <v>0.13207547169811321</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>78</v>
       </c>
@@ -2751,19 +3736,31 @@
         <v>21</v>
       </c>
       <c r="E80">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>7.8875518252603909E-3</v>
       </c>
       <c r="F80">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>5.8651026392961877E-3</v>
       </c>
       <c r="G80">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>2.1235716452624128E-3</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I80">
+        <f t="shared" si="13"/>
+        <v>0.49681528662420382</v>
+      </c>
+      <c r="J80">
+        <f t="shared" si="14"/>
+        <v>0.36942675159235666</v>
+      </c>
+      <c r="K80">
+        <f t="shared" si="15"/>
+        <v>0.13375796178343949</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>78</v>
       </c>
@@ -2774,19 +3771,31 @@
         <v>19</v>
       </c>
       <c r="E81">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>8.0462141530843814E-3</v>
       </c>
       <c r="F81">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>5.8799257272539717E-3</v>
       </c>
       <c r="G81">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1.9599752424179907E-3</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I81">
+        <f t="shared" si="13"/>
+        <v>0.50649350649350644</v>
+      </c>
+      <c r="J81">
+        <f t="shared" si="14"/>
+        <v>0.37012987012987014</v>
+      </c>
+      <c r="K81">
+        <f t="shared" si="15"/>
+        <v>0.12337662337662338</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>79</v>
       </c>
@@ -2797,19 +3806,31 @@
         <v>21</v>
       </c>
       <c r="E82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>7.7732952868247562E-3</v>
       </c>
       <c r="F82">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>5.8053724294007672E-3</v>
       </c>
       <c r="G82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>2.0663190002951884E-3</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I82">
+        <f t="shared" si="13"/>
+        <v>0.49685534591194969</v>
+      </c>
+      <c r="J82">
+        <f t="shared" si="14"/>
+        <v>0.37106918238993708</v>
+      </c>
+      <c r="K82">
+        <f t="shared" si="15"/>
+        <v>0.13207547169811321</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>77</v>
       </c>
@@ -2820,19 +3841,31 @@
         <v>20</v>
       </c>
       <c r="E83">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>8.1352350765979929E-3</v>
       </c>
       <c r="F83">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>5.9165346011621767E-3</v>
       </c>
       <c r="G83">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>2.1130480718436345E-3</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I83">
+        <f t="shared" si="13"/>
+        <v>0.50326797385620914</v>
+      </c>
+      <c r="J83">
+        <f t="shared" si="14"/>
+        <v>0.36601307189542481</v>
+      </c>
+      <c r="K83">
+        <f t="shared" si="15"/>
+        <v>0.13071895424836602</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>78</v>
       </c>
@@ -2843,19 +3876,31 @@
         <v>20</v>
       </c>
       <c r="E84">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>7.920389926888708E-3</v>
       </c>
       <c r="F84">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>5.889520714865963E-3</v>
       </c>
       <c r="G84">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>2.0308692120227455E-3</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I84">
+        <f t="shared" si="13"/>
+        <v>0.5</v>
+      </c>
+      <c r="J84">
+        <f t="shared" si="14"/>
+        <v>0.37179487179487181</v>
+      </c>
+      <c r="K84">
+        <f t="shared" si="15"/>
+        <v>0.12820512820512819</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>79</v>
       </c>
@@ -2866,19 +3911,31 @@
         <v>21</v>
       </c>
       <c r="E85">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>7.8638263985665938E-3</v>
       </c>
       <c r="F85">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>5.7734421660362335E-3</v>
       </c>
       <c r="G85">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>2.0903842325303602E-3</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I85">
+        <f t="shared" si="13"/>
+        <v>0.5</v>
+      </c>
+      <c r="J85">
+        <f t="shared" si="14"/>
+        <v>0.36708860759493672</v>
+      </c>
+      <c r="K85">
+        <f t="shared" si="15"/>
+        <v>0.13291139240506328</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>85</v>
       </c>
@@ -2889,19 +3946,31 @@
         <v>24</v>
       </c>
       <c r="E86">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>7.5341251551143415E-3</v>
       </c>
       <c r="F86">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>5.2295692253146609E-3</v>
       </c>
       <c r="G86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>2.1272823967381669E-3</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I86">
+        <f t="shared" si="13"/>
+        <v>0.50595238095238093</v>
+      </c>
+      <c r="J86">
+        <f t="shared" si="14"/>
+        <v>0.35119047619047616</v>
+      </c>
+      <c r="K86">
+        <f t="shared" si="15"/>
+        <v>0.14285714285714285</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>76</v>
       </c>
@@ -2912,19 +3981,31 @@
         <v>19</v>
       </c>
       <c r="E87">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>8.1958373773320398E-3</v>
       </c>
       <c r="F87">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>6.0390380675078188E-3</v>
       </c>
       <c r="G87">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>2.04895934433301E-3</v>
       </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I87">
+        <f t="shared" si="13"/>
+        <v>0.50331125827814571</v>
+      </c>
+      <c r="J87">
+        <f t="shared" si="14"/>
+        <v>0.37086092715231789</v>
+      </c>
+      <c r="K87">
+        <f t="shared" si="15"/>
+        <v>0.12582781456953643</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>77</v>
       </c>
@@ -2935,19 +4016,31 @@
         <v>19</v>
       </c>
       <c r="E88">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>8.2662372517444977E-3</v>
       </c>
       <c r="F88">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>5.9044551798174989E-3</v>
       </c>
       <c r="G88">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>2.0397208803005903E-3</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I88">
+        <f t="shared" si="13"/>
+        <v>0.50993377483443714</v>
+      </c>
+      <c r="J88">
+        <f t="shared" si="14"/>
+        <v>0.36423841059602646</v>
+      </c>
+      <c r="K88">
+        <f t="shared" si="15"/>
+        <v>0.12582781456953643</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>76</v>
       </c>
@@ -2958,19 +4051,31 @@
         <v>18</v>
       </c>
       <c r="E89">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>8.3287671232876708E-3</v>
       </c>
       <c r="F89">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>6.0273972602739728E-3</v>
       </c>
       <c r="G89">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1.9726027397260273E-3</v>
       </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I89">
+        <f t="shared" si="13"/>
+        <v>0.51006711409395977</v>
+      </c>
+      <c r="J89">
+        <f t="shared" si="14"/>
+        <v>0.36912751677852351</v>
+      </c>
+      <c r="K89">
+        <f t="shared" si="15"/>
+        <v>0.12080536912751678</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>79</v>
       </c>
@@ -2981,16 +4086,28 @@
         <v>21</v>
       </c>
       <c r="E90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>7.8638263985665938E-3</v>
       </c>
       <c r="F90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>5.7734421660362335E-3</v>
       </c>
       <c r="G90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>2.0903842325303602E-3</v>
+      </c>
+      <c r="I90">
+        <f t="shared" si="13"/>
+        <v>0.5</v>
+      </c>
+      <c r="J90">
+        <f t="shared" si="14"/>
+        <v>0.36708860759493672</v>
+      </c>
+      <c r="K90">
+        <f t="shared" si="15"/>
+        <v>0.13291139240506328</v>
       </c>
     </row>
   </sheetData>
